--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.49796976217058</v>
+        <v>9.01842008635272</v>
       </c>
       <c r="D2" t="n">
-        <v>14.82966660381989</v>
+        <v>2.409820823120732</v>
       </c>
       <c r="E2" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F2" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.46434550254889</v>
+        <v>3.812956144164195</v>
       </c>
       <c r="D3" t="n">
-        <v>13.73302668561718</v>
+        <v>2.231616836412792</v>
       </c>
       <c r="E3" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F3" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.197616422235704</v>
+        <v>1.169612668613302</v>
       </c>
       <c r="D4" t="n">
-        <v>16.71409917139153</v>
+        <v>2.716041115351124</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F4" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.23306739956833</v>
+        <v>3.775373452429855</v>
       </c>
       <c r="D5" t="n">
-        <v>7.113519685789228</v>
+        <v>1.15594694894075</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F5" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.50882392484711</v>
+        <v>6.907683887787656</v>
       </c>
       <c r="D6" t="n">
-        <v>29.22483194828982</v>
+        <v>4.749035191597097</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F6" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.51449992431381</v>
+        <v>8.371106237700994</v>
       </c>
       <c r="D7" t="n">
-        <v>14.57737973711325</v>
+        <v>2.368824207280903</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F7" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.6649845402676</v>
+        <v>7.583059987793485</v>
       </c>
       <c r="D8" t="n">
-        <v>32.68409399080844</v>
+        <v>5.311165273506371</v>
       </c>
       <c r="E8" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F8" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.23367325439085</v>
+        <v>5.075471903838514</v>
       </c>
       <c r="D9" t="n">
-        <v>21.70829334609241</v>
+        <v>3.527597668740017</v>
       </c>
       <c r="E9" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F9" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.88558103542889</v>
+        <v>6.318906918257195</v>
       </c>
       <c r="D10" t="n">
-        <v>38.10527089086583</v>
+        <v>6.192106519765698</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F10" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.49648450826481</v>
+        <v>7.555678732593033</v>
       </c>
       <c r="D11" t="n">
-        <v>42.60575078554537</v>
+        <v>6.923434502651123</v>
       </c>
       <c r="E11" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F11" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.03107188989507</v>
+        <v>6.99254918210795</v>
       </c>
       <c r="D12" t="n">
-        <v>39.24601890638081</v>
+        <v>6.377478072286882</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F12" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.59348316211991</v>
+        <v>5.296441013844485</v>
       </c>
       <c r="D13" t="n">
-        <v>30.58007787618936</v>
+        <v>4.969262654880771</v>
       </c>
       <c r="E13" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F13" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.83095462003193</v>
+        <v>6.310030125755189</v>
       </c>
       <c r="D14" t="n">
-        <v>36.33739392786116</v>
+        <v>5.904826513277439</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F14" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.35628479886213</v>
+        <v>8.020396279815095</v>
       </c>
       <c r="D15" t="n">
-        <v>48.15877747570009</v>
+        <v>7.825801339801266</v>
       </c>
       <c r="E15" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F15" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>50.77144447350227</v>
+        <v>8.250359726944119</v>
       </c>
       <c r="D16" t="n">
-        <v>35.28879967802884</v>
+        <v>5.734429947679687</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F16" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>67.14488741252364</v>
+        <v>10.91104420453509</v>
       </c>
       <c r="D17" t="n">
-        <v>60.88634241376649</v>
+        <v>9.894030642237054</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F17" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.95408899613444</v>
+        <v>6.492539461871847</v>
       </c>
       <c r="D18" t="n">
-        <v>41.06087940582582</v>
+        <v>6.672392903446696</v>
       </c>
       <c r="E18" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F18" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.22596428469812</v>
+        <v>7.024219196263445</v>
       </c>
       <c r="D19" t="n">
-        <v>35.70740797638108</v>
+        <v>5.802453796161926</v>
       </c>
       <c r="E19" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F19" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.9112554530854</v>
+        <v>6.648079011126378</v>
       </c>
       <c r="D20" t="n">
-        <v>39.23334641430553</v>
+        <v>6.375418792324648</v>
       </c>
       <c r="E20" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F20" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>37.48417323757043</v>
+        <v>6.091178151105195</v>
       </c>
       <c r="D21" t="n">
-        <v>31.4448809709776</v>
+        <v>5.10979315778386</v>
       </c>
       <c r="E21" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F21" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>67.60582984804898</v>
+        <v>10.98594735030796</v>
       </c>
       <c r="D22" t="n">
-        <v>60.43418985737251</v>
+        <v>9.820555851823032</v>
       </c>
       <c r="E22" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F22" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>51.50138624312572</v>
+        <v>8.368975264507929</v>
       </c>
       <c r="D23" t="n">
-        <v>43.77449399067348</v>
+        <v>7.11335527348444</v>
       </c>
       <c r="E23" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F23" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>61.49096080577021</v>
+        <v>9.992281130937659</v>
       </c>
       <c r="D24" t="n">
-        <v>53.89699281174951</v>
+        <v>8.758261331909296</v>
       </c>
       <c r="E24" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F24" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>73.43430411420015</v>
+        <v>11.93307441855752</v>
       </c>
       <c r="D25" t="n">
-        <v>72.52826393316332</v>
+        <v>11.78584288913904</v>
       </c>
       <c r="E25" t="n">
-        <v>14.7490793282637</v>
+        <v>2.396725390842851</v>
       </c>
       <c r="F25" t="n">
-        <v>15.93541982190305</v>
+        <v>2.589505721059245</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
